--- a/data/seed/portfolio/L-2024-7200/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-7200/vypiska_2026-07_09.xlsx
@@ -558,40 +558,40 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>5795000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>4396000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari XK</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>286060297</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000334691590001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №446</t>
+          <t>Оплата по с/ф №7045 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,40 +599,40 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>7668000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>25950000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari XK</t>
+          <t>Mehnat Polimer MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>286060297</t>
+          <t>367070284</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000334691590001</t>
+          <t>20208000218190892001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №107/26</t>
+          <t>Оплата за продукцию по договору №102/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -640,23 +640,23 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>15689000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>8669000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -666,14 +666,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №74/26</t>
+          <t>Shartnoma №291/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -682,32 +682,32 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32016000</v>
+        <v>7373000</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari XK</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>286060297</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000334691590001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1752</t>
+          <t>Оплата за товары согласно с/ф №6301</t>
         </is>
       </c>
     </row>
@@ -724,31 +724,31 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>19027000</v>
+        <v>27202000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Mehnat Polimer MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>367070284</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000218190892001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №653 06.07.2026, QQS bilan</t>
+          <t>SHARTNOMA №257/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>4051000</v>
+        <v>2277000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4958 06.07.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №8303 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -804,33 +804,33 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>3648000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>3628000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>209752506</t>
+          <t>302262554</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000126708657001</t>
+          <t>20208000905321369001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2192</t>
+          <t>Оплата за транспортные услуги по договору №108/26</t>
         </is>
       </c>
     </row>
@@ -846,32 +846,27 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7513000</v>
+        <v>8246000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nihol Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>305966269</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000703756703001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №138/26, QQS bilan</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
@@ -887,34 +882,39 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>8246000</v>
+        <v>16007000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Termiz Non MChJ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>216496752</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000524343512001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Оплата за товары согласно с/ф №1464</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>20090000</v>
+        <v>1324000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari XK</t>
+          <t>Oqtosh Qurilish MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>286060297</t>
+          <t>271319687</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000334691590001</t>
+          <t>20208000840643436001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -948,14 +948,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6654</t>
+          <t>Аренда помещения за июль, дог. №20/21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -965,38 +965,38 @@
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>13739000</v>
+        <v>4154000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>290972906</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000473876272001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №28/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №258/26 от 09.07.2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1005,39 +1005,34 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1324000</v>
+        <v>18700000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Urganch Qurilish AJ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>275049951</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7200)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000162552542001</t>
+          <t>16307000226889887417</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Kredit shartnomasi L-2024-7200 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1047,38 +1042,38 @@
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>21148000</v>
+        <v>10799000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7115</t>
+          <t>Оплата по счет-фактуре №6896 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1086,40 +1081,40 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>7721000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>3313000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Oydin Sut AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>297290694</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000387627213001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №93/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8070</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1127,40 +1122,40 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>3449000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>11301000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №23/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №9893</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,35 +1163,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>18700000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>30345000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7200)</t>
+          <t>Tong Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16307000226889887417</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7200 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за товар по с/ф №1918 от 14.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1204,40 +1204,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>6294000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>7524000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №189/26, QQS 12%</t>
+          <t>Предоплата за материалы по дог. №229/26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1245,40 +1245,40 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>7919000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>7852000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №31/26</t>
+          <t>Оплата за товар по счет-фактуре №6936 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1288,38 +1288,38 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>6252000</v>
+        <v>3496000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Shartnoma №198/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по с/ф №1051 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1328,39 +1328,39 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5623000</v>
+        <v>1124000</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nihol Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>305966269</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000703756703001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7356</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1369,39 +1369,39 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6202000</v>
+        <v>1124000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nihol Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>305966269</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000703756703001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №239/26</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1409,40 +1409,40 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>1124000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>4961000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Mahsulot uchun to'lov, shartn. №223/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1450,33 +1450,33 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>1124000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>2447000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>JSHDS IYUN OYI UCHUN</t>
+          <t>Оплата по счет-фактуре №5820 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1493,31 +1493,31 @@
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>20223000</v>
+        <v>4790000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №60/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №4032 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1534,31 +1534,31 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>12628000</v>
+        <v>3690000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Meva Eksport XK</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>262164967</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000275243435001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №53/26 от 20.07.2026</t>
+          <t>Предоплата за товар по договору №9/26 от 20.07.2026</t>
         </is>
       </c>
     </row>
@@ -1573,40 +1573,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>3556000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>28826000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5127</t>
+          <t>Оплата за товары согласно счет-фактуре №4813</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1614,40 +1614,40 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>34105000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>5294000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari XK</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>286060297</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000334691590001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №29/26</t>
+          <t>Предоплата за товар по договору №272/26 от 21.07.2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1655,33 +1655,33 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>2197000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>11256000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №248/26 ОТ 22.07.2026</t>
         </is>
       </c>
     </row>
@@ -1696,33 +1696,33 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>8947000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>6849000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>290972906</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000473876272001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8180 22.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №140/26</t>
         </is>
       </c>
     </row>
@@ -1737,33 +1737,33 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>3828000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>2199000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>290972906</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000473876272001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №67/26, QQS 12%</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
     </row>
@@ -1778,40 +1778,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>14293000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>7323000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Shartnoma №143/26 bo'yicha oldindan to'lov</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №1749</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,33 +1819,33 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>15413000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>9558000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Qo'qon Agro MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>254082532</t>
+          <t>302262554</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000843871465001</t>
+          <t>20208000905321369001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Shartnoma №144/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №130/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1862,31 +1862,31 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>5737000</v>
+        <v>3206000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №19/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №214/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1903,31 +1903,31 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>5331000</v>
+        <v>2652000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3203</t>
+          <t>Предоплата за товар по дог. №20/26 от 27.07.2026</t>
         </is>
       </c>
     </row>
@@ -1942,40 +1942,40 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>5308000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>828000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oqtosh Non MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>335670702</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000442181908001</t>
+          <t>20208000121858254001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №37/26, QQS 12%</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1983,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>828000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>5683000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000689752175001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за продукцию по договору №220/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2026,38 +2026,38 @@
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>2830000</v>
+        <v>3446000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Shartnoma №296/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7288 29.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2067,38 +2067,38 @@
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>7355000</v>
+        <v>3163000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>209752506</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000126708657001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №272/26 от 31.07.2026</t>
+          <t>Оплата за товар по счет-фактуре №3141 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2107,34 +2107,39 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>300000</v>
+        <v>48053000</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Termiz Non MChJ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>216496752</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000524343512001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Оплата за товары согласно счет-фактуре №5027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2144,21 +2149,21 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>7303000</v>
+        <v>4240000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Farovon Logistik XK</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>244947137</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000939593937001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2168,14 +2173,14 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SHARTNOMA №203/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата по счет-фактуре №7477 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2183,40 +2188,40 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>4665000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>6726000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>302262554</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000905321369001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2607 от 04.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №5986</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2225,39 +2230,34 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>4895000</v>
+        <v>300000</v>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari XK</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>286060297</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000334691590001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №202/26, QQS bilan</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2267,38 +2267,38 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>15360000</v>
+        <v>10266000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>209752506</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000126708657001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №89/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №2534 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2308,38 +2308,38 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>7551000</v>
+        <v>6777000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Mehnat Polimer MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>209752506</t>
+          <t>367070284</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000126708657001</t>
+          <t>20208000218190892001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №271/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №179/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2347,35 +2347,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>8100000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>6182000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Tong Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Оплата за продукцию по договору №274/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2385,38 +2390,38 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>8543000</v>
+        <v>2935000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3744 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3067 03.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2426,38 +2431,38 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>6306000</v>
+        <v>2733000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Shartnoma №219/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №2524 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2466,39 +2471,39 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>1301000</v>
+        <v>16585000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Urganch Qurilish AJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>275049951</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000162552542001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartnoma №72/21</t>
+          <t>Оплата за товары согласно с/ф №9286</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2506,40 +2511,40 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>16693000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>23738000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chirchiq Moy AJ</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>237797050</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000336051560001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №17/26</t>
+          <t>Оплата за товар по счет-фактуре №2767 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2547,35 +2552,40 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>18700000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>11377000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7200)</t>
+          <t>Tong Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>16307000226889887417</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7200 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Mahsulot uchun to'lov, shartn. №91/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2585,38 +2595,38 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>5677000</v>
+        <v>6831000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Shartnoma №220/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №1720 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2625,39 +2635,39 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>35097000</v>
+        <v>7431000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Toshkent Qurilish XK</t>
+          <t>Termiz Non MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>377029813</t>
+          <t>216496752</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000711236540001</t>
+          <t>20208000524343512001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №168/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №289/26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2666,39 +2676,34 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1105000</v>
+        <v>8100000</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2707,39 +2712,39 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>1105000</v>
+        <v>7114000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>302262554</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000905321369001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Materiallar uchun oldindan to'lov, shrtn. №11/26</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2748,22 +2753,22 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>6087000</v>
+        <v>1301000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari XK</t>
+          <t>Oqtosh Qurilish MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>286060297</t>
+          <t>271319687</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000334691590001</t>
+          <t>20208000840643436001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2773,14 +2778,14 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №167/26</t>
+          <t>Аренда помещения за август, дог. №20/21</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2789,39 +2794,34 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>11033000</v>
+        <v>18700000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>207366273</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7200)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>16307000226889887417</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №213</t>
+          <t>Kredit shartnomasi L-2024-7200 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2831,38 +2831,38 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>12358000</v>
+        <v>2640000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Durdona Poligraf MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>305399363</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000751612134001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1499</t>
+          <t>Оплата по счет-фактуре №8802 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2870,40 +2870,40 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>8824000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>4926000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Farovon Logistik XK</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>244947137</t>
+          <t>302262554</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000939593937001</t>
+          <t>20208000905321369001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6446 19.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №154/26</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2912,39 +2912,39 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>11887000</v>
+        <v>4947000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nihol Logistik MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>305966269</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000703756703001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №172/26</t>
+          <t>Tovarlar uchun to'lov h/f №5025</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2954,38 +2954,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>6998000</v>
+        <v>3424000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Shartnoma №221/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №204/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2993,40 +2993,40 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>5966000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>1105000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №981 за поставленный товар</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3035,39 +3035,39 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>7628000</v>
+        <v>1105000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №257/26</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3075,40 +3075,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>9949000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>4252000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Urganch Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>265240077</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000683161654001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Shartnoma №37/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №95/26</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3116,40 +3116,40 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>4450000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>12135000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>290972906</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000473876272001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №798 24.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №241/26</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3157,40 +3157,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>813000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>8134000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000689752175001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>ОПЛАТА ПО С/Ф №3846 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3198,40 +3198,40 @@
           <t>165</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>2065000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>3823000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>QQS IYUL 2026 UCHUN</t>
+          <t>Оплата по счет-фактуре №745 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3239,40 +3239,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>5203000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>3018000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №212/26</t>
+          <t>Оплата по счет-фактуре №2796 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3280,40 +3280,40 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>20770000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>3813000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Urganch Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>290972906</t>
+          <t>265240077</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000473876272001</t>
+          <t>20208000683161654001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura№7296 25.08.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №96/26</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3323,38 +3323,38 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>15144000</v>
+        <v>4941000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Durdona Poligraf MChJ</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>305399363</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000751612134001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5393 25.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №245/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3362,40 +3362,40 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>15618000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>5679000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>302262554</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000905321369001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №159/26 от 26.08.2026</t>
+          <t>Оплата за сырье по договору №143/26 от 19.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3405,38 +3405,38 @@
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>12082000</v>
+        <v>39893000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №216/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №296/26 от 20.08.2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3446,38 +3446,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>4560000</v>
+        <v>20053000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №108/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №866 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3485,18 +3485,23 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>8598000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Afrosiyob Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3506,14 +3511,14 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Mahsulot uchun to'lov, shartnoma №178/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3522,39 +3527,39 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>6011000</v>
+        <v>3989000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №3413</t>
+          <t>Предоплата за материалы по дог. №262/26</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3563,39 +3568,39 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>41119000</v>
+        <v>4019000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №297/26</t>
+          <t>Оплата за сырье по договору №82/26 от 20.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3603,40 +3608,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>2116000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>813000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>209752506</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000126708657001</t>
+          <t>20208000121858254001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Shartnoma №154/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3645,39 +3650,39 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>6480000</v>
+        <v>2112000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9768</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3685,40 +3690,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>1075000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>6263000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Qo'qon Agro MChJ</t>
+          <t>Omad Moy XK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>254082532</t>
+          <t>246551965</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000843871465001</t>
+          <t>20208000297032196001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Shartnoma №163/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartn. №130/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3726,23 +3731,23 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>4646000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>4324000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3752,14 +3757,14 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №112/26</t>
+          <t>Оплата за продукцию по договору №251/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3767,40 +3772,40 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>2439000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>15721000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №245/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №147/26</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3810,38 +3815,38 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>1948000</v>
+        <v>6342000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4060 04.09.2026, QQS bilan</t>
+          <t>Shartnoma №194/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3849,40 +3854,35 @@
           <t>181</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>13638000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oqtosh Non MChJ</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>335670702</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000442181908001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Shartnoma №189/26 bo'yicha oldindan to'lov</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3890,40 +3890,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>4656000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>302262554</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000905321369001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №228/26, QQS 12%</t>
+          <t>Оплата за сырье по дог. №165/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3931,40 +3931,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>1921000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>8238000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7123 07.09.2026, QQS BILAN</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №78/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3973,39 +3973,39 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>3307000</v>
+        <v>11284000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Lazzat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>302262554</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000905321369001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №211/26</t>
+          <t>Tovarlar uchun to'lov h/f №42</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4014,34 +4014,39 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>7954000</v>
+        <v>12007000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Omad Moy XK</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>246551965</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000297032196001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Оплата за транспортные услуги по дог. №177/26</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4049,40 +4054,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>5702000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>12487000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Urganch Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>265240077</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000683161654001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6503 08.09.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №52/26</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4092,38 +4097,38 @@
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>1546000</v>
+        <v>2644000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>209752506</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000126708657001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8545</t>
+          <t>Оплата за продукцию по договору №131/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4131,23 +4136,23 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>1641000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>1258000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nihol Logistik MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>305966269</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000703756703001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4157,14 +4162,14 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №38/26, QQS BILAN</t>
+          <t>Shartnoma №226/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4172,23 +4177,23 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>1953000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>18876000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nihol Logistik MChJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>305966269</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000703756703001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4198,14 +4203,14 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №123/26</t>
+          <t>Предоплата за товар по дог. №223/26 от 04.09.2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4213,40 +4218,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>2642000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>2467000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Omad Sut Mahsulotlari XK</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>286060297</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000334691590001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №229/26</t>
+          <t>Оплата за продукцию по договору №144/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4254,23 +4259,23 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>4052000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>1155000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4280,14 +4285,14 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №267/26, QQS bilan</t>
+          <t>Оплата за товар по с/ф №4060 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4295,23 +4300,23 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>7838000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>4585000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4321,14 +4326,14 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №228/26</t>
+          <t>Предоплата за товар по дог. №195/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4336,40 +4341,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>1024000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>1278000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Qo'qon Agro MChJ</t>
+          <t>Oqtosh Qurilish MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>254082532</t>
+          <t>271319687</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000843871465001</t>
+          <t>20208000840643436001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1112 09.09.2026, QQS bilan</t>
+          <t>Аренда помещения за сентябрь, дог. №20/21</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4377,40 +4382,35 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>922000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>7954000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>225614310</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5363 09.09.2026, QQS bilan</t>
+          <t>Avgust oyi uchun ish haqi, reestr №2739</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4419,39 +4419,39 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>1278000</v>
+        <v>12346000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Urganch Qurilish AJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>275049951</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000162552542001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №72/21</t>
+          <t>Предоплата за материалы по дог. №261/26</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4460,17 +4460,22 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>18700000</v>
+        <v>12992000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7200)</t>
+          <t>Zarafshon Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>16307000226889887417</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4480,14 +4485,14 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7200 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Предоплата за материалы по дог. №283/26</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4497,38 +4502,38 @@
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>42755000</v>
+        <v>7743000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Qo'qon Agro MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>254082532</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000843871465001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Shartnoma №185/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4115 08.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4538,38 +4543,38 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>1291000</v>
+        <v>83198000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Oqtosh Non MChJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>335670702</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000442181908001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun tolov h/f №645</t>
+          <t>Оплата за продукцию по договору №126/26, НДС12%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4577,23 +4582,23 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>10204000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>4065000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4603,14 +4608,14 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №91/26 от 11.09.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №213/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4618,40 +4623,35 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>5699000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>18700000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>209752506</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7200)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000126708657001</t>
+          <t>16307000226889887417</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №259/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-7200 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4661,38 +4661,38 @@
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>2034000</v>
+        <v>18139000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №142/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №224/26 от 11.09.2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4700,33 +4700,33 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>1500000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>11505000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5777 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №4257</t>
         </is>
       </c>
     </row>
@@ -4743,31 +4743,31 @@
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>1471000</v>
+        <v>1835000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>209752506</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000126708657001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4912 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №67/26 от 14.09.2026</t>
         </is>
       </c>
     </row>
@@ -4782,33 +4782,33 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>1085000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>989000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Оплата за продукцию по договору №289/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -4823,40 +4823,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>1085000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>767000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Tovar uchun to'lov, h/f №4912 14.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4866,38 +4866,38 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>27181000</v>
+        <v>719000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>209752506</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000126708657001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Shartnoma №243/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №2834 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4905,33 +4905,33 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>10443000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>38824000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>290972906</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000473876272001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4209 15.09.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №160/26</t>
         </is>
       </c>
     </row>
@@ -4948,31 +4948,31 @@
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>9948000</v>
+        <v>5695000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>290972906</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000473876272001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №208/26, QQS 12%</t>
+          <t>Оплата по с/ф №7967 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -4989,21 +4989,21 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>5711000</v>
+        <v>1635000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Oydin Sut AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>297290694</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000387627213001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7967</t>
+          <t>Оплата за продукцию по договору №208/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -5028,33 +5028,33 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>1313000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>1085000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Farovon Moy MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>209752506</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000126708657001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7462</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
     </row>
@@ -5069,40 +5069,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>998000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>1085000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Qo'qon Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>254082532</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000843871465001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4446</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5110,40 +5110,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>845000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>38197000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Qo'qon Agro MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>254082532</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000843871465001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №6231 15.09.2026, QQS BILAN</t>
+          <t>Оплата за транспортные услуги по дог. №107/26</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5151,40 +5151,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>1463000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>3837000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №162/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №117/26</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5194,38 +5194,38 @@
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>898000</v>
+        <v>2114000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Durdona Poligraf MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>305399363</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000751612134001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №257/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №129/26 от 21.09.2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5233,23 +5233,23 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>37365000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>1838000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №49/26</t>
+          <t>Shartnoma №219/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -5276,31 +5276,31 @@
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>1502000</v>
+        <v>887000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Shartnoma №259/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №173/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -5316,39 +5316,39 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>2868000</v>
+        <v>8673000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Denov Tur Servis AJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>212979018</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000853861902001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, sharn. №21/26</t>
+          <t>Предоплата за материалы по договору №23/26</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5357,32 +5357,32 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>36721000</v>
+        <v>2200000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Nihol Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>305966269</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000703756703001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №233/26, QQS bilan</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
     </row>
@@ -5399,38 +5399,38 @@
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>1312000</v>
+        <v>1981000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2333</t>
+          <t>Оплата по счет-фактуре №2333 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5438,40 +5438,40 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>798000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>5152000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000689752175001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата по счет-фактуре №9568 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5479,33 +5479,33 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>2149000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>1740000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Оплата за товар по счет-фактуре №1777 от 24.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -5522,38 +5522,38 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>3042000</v>
+        <v>1021000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7191</t>
+          <t>Оплата по счет-фактуре №7191 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5563,38 +5563,38 @@
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>1998000</v>
+        <v>2791000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Afrosiyob Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>339936367</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000161213470001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7294 за поставленный товар</t>
+          <t>Предоплата за товар по договору №256/26 от 25.09.2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5602,23 +5602,23 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>4249000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>2597000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nihol Logistik MChJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>305966269</t>
+          <t>294713749</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000703756703001</t>
+          <t>20208000959393774001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №29/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №173/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -5643,33 +5643,33 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>1917000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>798000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000121858254001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4115 от 25.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
     </row>
@@ -5684,23 +5684,23 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>4003000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>2550000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Tong Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>361431065</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000984074080001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5710,14 +5710,14 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №131/26</t>
+          <t>Оплата по счет-фактуре №7003 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,33 +5725,33 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>1557000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>17084000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Ziyo Logistik MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>285825403</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000910691126001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №10/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №50/26</t>
         </is>
       </c>
     </row>
@@ -5768,31 +5768,31 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>17188000</v>
+        <v>4862000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Afrosiyob Logistik MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>225614310</t>
+          <t>375250681</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000539840740001</t>
+          <t>20208000670865798001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3212</t>
+          <t>Предоплата за товар по договору №231/26 от 30.09.2026</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
         </is>
       </c>
     </row>
@@ -5844,32 +5844,32 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>16590000</v>
+        <v>3816000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Zarafshon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>207366273</t>
+          <t>235674339</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000796737826001</t>
+          <t>20208000692950079001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3942</t>
+          <t>Предоплата за материалы по договору №124/26</t>
         </is>
       </c>
     </row>
@@ -5880,10 +5880,10 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>541234000</v>
+        <v>549613000</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>534234000</v>
+        <v>542613000</v>
       </c>
     </row>
     <row r="142">
